--- a/pipeline/facility_extras.xlsx
+++ b/pipeline/facility_extras.xlsx
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>AdviniaCare</t>
+          <t>Centers Health Care</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3947,11 +3947,7 @@
           <t>corporate/investors</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3981,7 +3977,11 @@
           <t>ADVINIA</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>Closed January 2025, while it was being transferred to new owners. AdviniaCare never took it over.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">

--- a/pipeline/facility_extras.xlsx
+++ b/pipeline/facility_extras.xlsx
@@ -993,7 +993,11 @@
           <t>nonprofit</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Closed 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
